--- a/Extracted_data_analysis/temperate/Output-Transformed_data/summary_counts_question_1-3.xlsx
+++ b/Extracted_data_analysis/temperate/Output-Transformed_data/summary_counts_question_1-3.xlsx
@@ -585,6 +585,9 @@
     <t xml:space="preserve">Behaviour+Physiological+sex</t>
   </si>
   <si>
+    <t xml:space="preserve">Behaviour+Trophic+geneticSequences</t>
+  </si>
+  <si>
     <t xml:space="preserve">Biomass+Cover+Density+Diversity+Size</t>
   </si>
   <si>
@@ -630,9 +633,6 @@
     <t xml:space="preserve">Cover</t>
   </si>
   <si>
-    <t xml:space="preserve">Cover+ Diversity+Morphological</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cover+ALDFGs+Health+Litter</t>
   </si>
   <si>
@@ -774,7 +774,7 @@
     <t xml:space="preserve">Density+Diversity+Habitat+Size</t>
   </si>
   <si>
-    <t xml:space="preserve">Density+Diversity+sample</t>
+    <t xml:space="preserve">Density+Diversity+taxo</t>
   </si>
   <si>
     <t xml:space="preserve">Density+geneticSequences</t>
@@ -1473,7 +1473,7 @@
         <v>22</v>
       </c>
       <c r="C2" t="n">
-        <v>4.35</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="3">
@@ -1495,7 +1495,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="5">
@@ -1506,7 +1506,7 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="6">
@@ -1514,10 +1514,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C6" t="n">
-        <v>50.59</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="7">
@@ -1525,10 +1525,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C7" t="n">
-        <v>31.82</v>
+        <v>32.02</v>
       </c>
     </row>
     <row r="8">
@@ -1539,7 +1539,7 @@
         <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="9">
@@ -1550,7 +1550,7 @@
         <v>35</v>
       </c>
       <c r="C9" t="n">
-        <v>6.92</v>
+        <v>6.88</v>
       </c>
     </row>
   </sheetData>
@@ -1583,7 +1583,7 @@
         <v>189</v>
       </c>
       <c r="C2" t="n">
-        <v>36.07</v>
+        <v>35.86</v>
       </c>
     </row>
     <row r="3">
@@ -1591,10 +1591,10 @@
         <v>12</v>
       </c>
       <c r="B3" t="n">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C3" t="n">
-        <v>54.77</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="4">
@@ -1605,7 +1605,7 @@
         <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>9.16</v>
+        <v>9.11</v>
       </c>
     </row>
   </sheetData>
@@ -1638,7 +1638,7 @@
         <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="3">
@@ -1660,7 +1660,7 @@
         <v>56</v>
       </c>
       <c r="C4" t="n">
-        <v>10.53</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="5">
@@ -1671,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="6">
@@ -1693,7 +1693,7 @@
         <v>35</v>
       </c>
       <c r="C7" t="n">
-        <v>6.58</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="8">
@@ -1701,10 +1701,10 @@
         <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C8" t="n">
-        <v>78.57</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="9">
@@ -1770,7 +1770,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="3">
@@ -1781,7 +1781,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="4">
@@ -1789,10 +1789,10 @@
         <v>27</v>
       </c>
       <c r="B4" t="n">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C4" t="n">
-        <v>93.88</v>
+        <v>93.91</v>
       </c>
     </row>
   </sheetData>
@@ -1825,7 +1825,7 @@
         <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>38.43</v>
+        <v>38.21</v>
       </c>
     </row>
     <row r="3">
@@ -1836,7 +1836,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="4">
@@ -1869,7 +1869,7 @@
         <v>34</v>
       </c>
       <c r="C6" t="n">
-        <v>6.5</v>
+        <v>6.46</v>
       </c>
     </row>
     <row r="7">
@@ -1877,10 +1877,10 @@
         <v>34</v>
       </c>
       <c r="B7" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>19.5</v>
+        <v>19.77</v>
       </c>
     </row>
     <row r="8">
@@ -1902,7 +1902,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="10">
@@ -1910,10 +1910,10 @@
         <v>37</v>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C10" t="n">
-        <v>19.31</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="11">
@@ -1924,7 +1924,7 @@
         <v>51</v>
       </c>
       <c r="C11" t="n">
-        <v>9.75</v>
+        <v>9.7</v>
       </c>
     </row>
   </sheetData>
@@ -1957,7 +1957,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="3">
@@ -1968,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="4">
@@ -1979,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="5">
@@ -1990,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="6">
@@ -2001,7 +2001,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="7">
@@ -2012,7 +2012,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="8">
@@ -2023,7 +2023,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="9">
@@ -2034,7 +2034,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -2045,7 +2045,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="11">
@@ -2056,7 +2056,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12">
@@ -2067,7 +2067,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="13">
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="14">
@@ -2089,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15">
@@ -2100,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="16">
@@ -2111,7 +2111,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="17">
@@ -2122,7 +2122,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="18">
@@ -2133,7 +2133,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="19">
@@ -2144,7 +2144,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20">
@@ -2155,7 +2155,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="21">
@@ -2166,7 +2166,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22">
@@ -2177,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="23">
@@ -2188,7 +2188,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="24">
@@ -2199,7 +2199,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25">
@@ -2210,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="26">
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="27">
@@ -2232,7 +2232,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="28">
@@ -2265,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="31">
@@ -2276,7 +2276,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="32">
@@ -2287,7 +2287,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="33">
@@ -2298,7 +2298,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="34">
@@ -2320,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="36">
@@ -2331,7 +2331,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="37">
@@ -2342,7 +2342,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="38">
@@ -2353,7 +2353,7 @@
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="39">
@@ -2364,7 +2364,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
@@ -2375,7 +2375,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
@@ -2386,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
@@ -2397,7 +2397,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="43">
@@ -2408,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="44">
@@ -2430,7 +2430,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="46">
@@ -2441,7 +2441,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="47">
@@ -2452,7 +2452,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="48">
@@ -2463,7 +2463,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="49">
@@ -2474,7 +2474,7 @@
         <v>1</v>
       </c>
       <c r="C49" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="50">
@@ -2485,7 +2485,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="51">
@@ -2496,7 +2496,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="52">
@@ -2507,7 +2507,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="53">
@@ -2518,7 +2518,7 @@
         <v>17</v>
       </c>
       <c r="C53" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="54">
@@ -2529,7 +2529,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="55">
@@ -2540,7 +2540,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="56">
@@ -2551,7 +2551,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="57">
@@ -2559,10 +2559,10 @@
         <v>95</v>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57" t="n">
-        <v>0.37</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="58">
@@ -2573,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="59">
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="62">
@@ -2617,7 +2617,7 @@
         <v>1</v>
       </c>
       <c r="C62" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="63">
@@ -2639,7 +2639,7 @@
         <v>1</v>
       </c>
       <c r="C64" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="65">
@@ -2650,7 +2650,7 @@
         <v>10</v>
       </c>
       <c r="C65" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="66">
@@ -2661,7 +2661,7 @@
         <v>1</v>
       </c>
       <c r="C66" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="67">
@@ -2672,7 +2672,7 @@
         <v>1</v>
       </c>
       <c r="C67" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="68">
@@ -2683,7 +2683,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="69">
@@ -2694,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="C69" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="70">
@@ -2705,7 +2705,7 @@
         <v>1</v>
       </c>
       <c r="C70" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="71">
@@ -2716,7 +2716,7 @@
         <v>1</v>
       </c>
       <c r="C71" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="72">
@@ -2727,7 +2727,7 @@
         <v>9</v>
       </c>
       <c r="C72" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="73">
@@ -2738,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="C73" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="74">
@@ -2760,7 +2760,7 @@
         <v>1</v>
       </c>
       <c r="C75" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="76">
@@ -2779,10 +2779,10 @@
         <v>115</v>
       </c>
       <c r="B77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" t="n">
-        <v>1.11</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="78">
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="C78" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="79">
@@ -2815,7 +2815,7 @@
         <v>1</v>
       </c>
       <c r="C80" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="81">
@@ -2826,7 +2826,7 @@
         <v>1</v>
       </c>
       <c r="C81" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="82">
@@ -2848,7 +2848,7 @@
         <v>1</v>
       </c>
       <c r="C83" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="84">
@@ -2870,7 +2870,7 @@
         <v>1</v>
       </c>
       <c r="C85" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="86">
@@ -2881,7 +2881,7 @@
         <v>1</v>
       </c>
       <c r="C86" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="87">
@@ -2903,7 +2903,7 @@
         <v>1</v>
       </c>
       <c r="C88" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="89">
@@ -2914,7 +2914,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="90">
@@ -2925,7 +2925,7 @@
         <v>1</v>
       </c>
       <c r="C90" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="91">
@@ -2936,7 +2936,7 @@
         <v>1</v>
       </c>
       <c r="C91" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="92">
@@ -2947,7 +2947,7 @@
         <v>1</v>
       </c>
       <c r="C92" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="93">
@@ -2958,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="C93" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="94">
@@ -2969,7 +2969,7 @@
         <v>1</v>
       </c>
       <c r="C94" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="95">
@@ -2980,7 +2980,7 @@
         <v>1</v>
       </c>
       <c r="C95" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="96">
@@ -2991,7 +2991,7 @@
         <v>1</v>
       </c>
       <c r="C96" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="97">
@@ -3002,7 +3002,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="98">
@@ -3013,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="C98" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="99">
@@ -3024,7 +3024,7 @@
         <v>24</v>
       </c>
       <c r="C99" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="100">
@@ -3035,7 +3035,7 @@
         <v>1</v>
       </c>
       <c r="C100" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="101">
@@ -3046,7 +3046,7 @@
         <v>1</v>
       </c>
       <c r="C101" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="102">
@@ -3079,7 +3079,7 @@
         <v>1</v>
       </c>
       <c r="C104" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="105">
@@ -3090,7 +3090,7 @@
         <v>1</v>
       </c>
       <c r="C105" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="106">
@@ -3101,7 +3101,7 @@
         <v>1</v>
       </c>
       <c r="C106" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="107">
@@ -3112,7 +3112,7 @@
         <v>1</v>
       </c>
       <c r="C107" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="108">
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="C109" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="110">
@@ -3145,7 +3145,7 @@
         <v>1</v>
       </c>
       <c r="C110" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="111">
@@ -3156,7 +3156,7 @@
         <v>1</v>
       </c>
       <c r="C111" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="112">
@@ -3167,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="C112" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="113">
@@ -3178,7 +3178,7 @@
         <v>1</v>
       </c>
       <c r="C113" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="114">
@@ -3189,7 +3189,7 @@
         <v>1</v>
       </c>
       <c r="C114" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="115">
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="C116" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="117">
@@ -3222,7 +3222,7 @@
         <v>5</v>
       </c>
       <c r="C117" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="118">
@@ -3233,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="119">
@@ -3255,7 +3255,7 @@
         <v>1</v>
       </c>
       <c r="C120" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="121">
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="C121" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="122">
@@ -3277,7 +3277,7 @@
         <v>1</v>
       </c>
       <c r="C122" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="123">
@@ -3288,7 +3288,7 @@
         <v>1</v>
       </c>
       <c r="C123" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="124">
@@ -3299,7 +3299,7 @@
         <v>1</v>
       </c>
       <c r="C124" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="125">
@@ -3310,7 +3310,7 @@
         <v>1</v>
       </c>
       <c r="C125" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="126">
@@ -3321,7 +3321,7 @@
         <v>1</v>
       </c>
       <c r="C126" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="127">
@@ -3332,7 +3332,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="128">
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
       <c r="C128" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="129">
@@ -3354,7 +3354,7 @@
         <v>1</v>
       </c>
       <c r="C129" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="130">
@@ -3365,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="C130" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="131">
@@ -3376,7 +3376,7 @@
         <v>1</v>
       </c>
       <c r="C131" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="132">
@@ -3387,7 +3387,7 @@
         <v>1</v>
       </c>
       <c r="C132" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="133">
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="C133" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="134">
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="C134" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="135">
@@ -3420,7 +3420,7 @@
         <v>1</v>
       </c>
       <c r="C135" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="136">
@@ -3431,7 +3431,7 @@
         <v>1</v>
       </c>
       <c r="C136" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="137">
@@ -3442,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="C137" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="138">
@@ -3464,7 +3464,7 @@
         <v>10</v>
       </c>
       <c r="C139" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="140">
@@ -3486,7 +3486,7 @@
         <v>1</v>
       </c>
       <c r="C141" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="142">
@@ -3497,7 +3497,7 @@
         <v>1</v>
       </c>
       <c r="C142" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="143">
@@ -3508,7 +3508,7 @@
         <v>1</v>
       </c>
       <c r="C143" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="144">
@@ -3519,7 +3519,7 @@
         <v>1</v>
       </c>
       <c r="C144" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="145">
@@ -3530,7 +3530,7 @@
         <v>1</v>
       </c>
       <c r="C145" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="146">
@@ -3541,7 +3541,7 @@
         <v>1</v>
       </c>
       <c r="C146" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="147">
@@ -3552,7 +3552,7 @@
         <v>1</v>
       </c>
       <c r="C147" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="148">
@@ -3563,7 +3563,7 @@
         <v>1</v>
       </c>
       <c r="C148" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="149">
@@ -3574,7 +3574,7 @@
         <v>1</v>
       </c>
       <c r="C149" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="150">
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="C150" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="151">
@@ -3596,7 +3596,7 @@
         <v>1</v>
       </c>
       <c r="C151" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="152">
@@ -3607,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="153">
@@ -3618,7 +3618,7 @@
         <v>1</v>
       </c>
       <c r="C153" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="154">
@@ -3629,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="C154" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="155">
@@ -3640,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="C155" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="156">
@@ -3651,7 +3651,7 @@
         <v>1</v>
       </c>
       <c r="C156" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="157">
@@ -3662,7 +3662,7 @@
         <v>1</v>
       </c>
       <c r="C157" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="158">
@@ -3673,7 +3673,7 @@
         <v>1</v>
       </c>
       <c r="C158" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="159">
@@ -3681,10 +3681,10 @@
         <v>197</v>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" t="n">
-        <v>0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="160">
@@ -3692,10 +3692,10 @@
         <v>198</v>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
-        <v>0.19</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="161">
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="C161" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="162">
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="C162" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="163">
@@ -3728,7 +3728,7 @@
         <v>1</v>
       </c>
       <c r="C163" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="164">
@@ -3736,10 +3736,10 @@
         <v>202</v>
       </c>
       <c r="B164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>0.56</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="165">
@@ -3747,10 +3747,10 @@
         <v>203</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C165" t="n">
-        <v>0.19</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="166">
@@ -3761,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="C166" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="167">
@@ -3772,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="C167" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="168">
@@ -3794,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="C169" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="170">
@@ -3805,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="C170" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="171">
@@ -3827,7 +3827,7 @@
         <v>1</v>
       </c>
       <c r="C172" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="173">
@@ -3838,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="C173" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="174">
@@ -3849,7 +3849,7 @@
         <v>1</v>
       </c>
       <c r="C174" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="175">
@@ -3860,7 +3860,7 @@
         <v>1</v>
       </c>
       <c r="C175" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="176">
@@ -3871,7 +3871,7 @@
         <v>1</v>
       </c>
       <c r="C176" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="177">
@@ -3882,7 +3882,7 @@
         <v>1</v>
       </c>
       <c r="C177" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="178">
@@ -3893,7 +3893,7 @@
         <v>1</v>
       </c>
       <c r="C178" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="179">
@@ -3904,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="C179" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="180">
@@ -3926,7 +3926,7 @@
         <v>23</v>
       </c>
       <c r="C181" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="182">
@@ -3937,7 +3937,7 @@
         <v>1</v>
       </c>
       <c r="C182" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="183">
@@ -3970,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="C185" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="186">
@@ -3981,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="C186" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="187">
@@ -4003,7 +4003,7 @@
         <v>1</v>
       </c>
       <c r="C188" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="189">
@@ -4014,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="C189" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="190">
@@ -4022,10 +4022,10 @@
         <v>228</v>
       </c>
       <c r="B190" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C190" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="191">
@@ -4047,7 +4047,7 @@
         <v>1</v>
       </c>
       <c r="C192" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="193">
@@ -4058,7 +4058,7 @@
         <v>1</v>
       </c>
       <c r="C193" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="194">
@@ -4069,7 +4069,7 @@
         <v>3</v>
       </c>
       <c r="C194" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="195">
@@ -4080,7 +4080,7 @@
         <v>1</v>
       </c>
       <c r="C195" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="196">
@@ -4102,7 +4102,7 @@
         <v>5</v>
       </c>
       <c r="C197" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="198">
@@ -4113,7 +4113,7 @@
         <v>1</v>
       </c>
       <c r="C198" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="199">
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="C199" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="200">
@@ -4132,10 +4132,10 @@
         <v>238</v>
       </c>
       <c r="B200" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C200" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="201">
@@ -4146,7 +4146,7 @@
         <v>1</v>
       </c>
       <c r="C201" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="202">
@@ -4157,7 +4157,7 @@
         <v>3</v>
       </c>
       <c r="C202" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="203">
@@ -4168,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="C203" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="204">
@@ -4179,7 +4179,7 @@
         <v>1</v>
       </c>
       <c r="C204" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="205">
@@ -4190,7 +4190,7 @@
         <v>1</v>
       </c>
       <c r="C205" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="206">
@@ -4212,7 +4212,7 @@
         <v>1</v>
       </c>
       <c r="C207" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="208">
@@ -4234,7 +4234,7 @@
         <v>1</v>
       </c>
       <c r="C209" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="210">
@@ -4245,7 +4245,7 @@
         <v>1</v>
       </c>
       <c r="C210" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="211">
@@ -4256,7 +4256,7 @@
         <v>3</v>
       </c>
       <c r="C211" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="212">
@@ -4267,7 +4267,7 @@
         <v>1</v>
       </c>
       <c r="C212" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="213">
@@ -4278,7 +4278,7 @@
         <v>1</v>
       </c>
       <c r="C213" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="214">
@@ -4289,7 +4289,7 @@
         <v>1</v>
       </c>
       <c r="C214" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="215">
@@ -4300,7 +4300,7 @@
         <v>1</v>
       </c>
       <c r="C215" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="216">
@@ -4311,7 +4311,7 @@
         <v>1</v>
       </c>
       <c r="C216" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="217">
@@ -4322,7 +4322,7 @@
         <v>3</v>
       </c>
       <c r="C217" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="218">
@@ -4333,7 +4333,7 @@
         <v>1</v>
       </c>
       <c r="C218" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="219">
@@ -4355,7 +4355,7 @@
         <v>1</v>
       </c>
       <c r="C220" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="221">
@@ -4366,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="C221" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="222">
@@ -4377,7 +4377,7 @@
         <v>1</v>
       </c>
       <c r="C222" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="223">
@@ -4388,7 +4388,7 @@
         <v>1</v>
       </c>
       <c r="C223" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="224">
@@ -4399,7 +4399,7 @@
         <v>1</v>
       </c>
       <c r="C224" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="225">
@@ -4410,7 +4410,7 @@
         <v>1</v>
       </c>
       <c r="C225" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="226">
@@ -4421,7 +4421,7 @@
         <v>5</v>
       </c>
       <c r="C226" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="227">
@@ -4432,7 +4432,7 @@
         <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="228">
@@ -4443,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="C228" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="229">
@@ -4451,10 +4451,10 @@
         <v>267</v>
       </c>
       <c r="B229" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C229" t="n">
-        <v>2.04</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="230">
@@ -4465,7 +4465,7 @@
         <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="231">
@@ -4476,7 +4476,7 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="232">
@@ -4498,7 +4498,7 @@
         <v>7</v>
       </c>
       <c r="C233" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="234">
@@ -4509,7 +4509,7 @@
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="235">
@@ -4520,7 +4520,7 @@
         <v>3</v>
       </c>
       <c r="C235" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="236">
@@ -4531,7 +4531,7 @@
         <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="237">
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="C238" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="239">
@@ -4564,7 +4564,7 @@
         <v>1</v>
       </c>
       <c r="C239" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="240">
@@ -4597,7 +4597,7 @@
         <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="243">
@@ -4608,7 +4608,7 @@
         <v>1</v>
       </c>
       <c r="C243" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="244">
@@ -4619,7 +4619,7 @@
         <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="245">
@@ -4641,7 +4641,7 @@
         <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="247">
@@ -4652,7 +4652,7 @@
         <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="248">
@@ -4663,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="249">
@@ -4674,7 +4674,7 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="250">
@@ -4685,7 +4685,7 @@
         <v>14</v>
       </c>
       <c r="C250" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="251">
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="252">
@@ -4707,7 +4707,7 @@
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="253">
@@ -4718,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="254">
@@ -4729,7 +4729,7 @@
         <v>1</v>
       </c>
       <c r="C254" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="255">
@@ -4740,7 +4740,7 @@
         <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="256">
@@ -4751,7 +4751,7 @@
         <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="257">
@@ -4762,7 +4762,7 @@
         <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="258">
@@ -4773,7 +4773,7 @@
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="259">
@@ -4784,7 +4784,7 @@
         <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="260">
@@ -4795,7 +4795,7 @@
         <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="261">
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="C261" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="262">
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="263">
@@ -4828,7 +4828,7 @@
         <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="264">
@@ -4839,7 +4839,7 @@
         <v>9</v>
       </c>
       <c r="C264" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="265">
@@ -4861,7 +4861,7 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="267">
@@ -4872,7 +4872,7 @@
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="268">
@@ -4894,7 +4894,7 @@
         <v>3</v>
       </c>
       <c r="C269" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="270">
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="271">
@@ -4916,7 +4916,7 @@
         <v>1</v>
       </c>
       <c r="C271" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="272">
@@ -4927,7 +4927,7 @@
         <v>1</v>
       </c>
       <c r="C272" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="273">
@@ -4938,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="C273" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="274">
@@ -4949,7 +4949,7 @@
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="275">
@@ -4960,7 +4960,7 @@
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="276">
@@ -4971,7 +4971,7 @@
         <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="277">
@@ -4993,7 +4993,7 @@
         <v>3</v>
       </c>
       <c r="C278" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="279">
@@ -5004,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="280">
@@ -5015,7 +5015,7 @@
         <v>3</v>
       </c>
       <c r="C280" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="281">
@@ -5026,7 +5026,7 @@
         <v>1</v>
       </c>
       <c r="C281" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="282">
@@ -5037,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="283">
@@ -5048,7 +5048,7 @@
         <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
   </sheetData>
@@ -5081,7 +5081,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="3">
@@ -5092,7 +5092,7 @@
         <v>69</v>
       </c>
       <c r="C3" t="n">
-        <v>12.8</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="4">
@@ -5114,7 +5114,7 @@
         <v>41</v>
       </c>
       <c r="C5" t="n">
-        <v>7.61</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="6">
@@ -5136,7 +5136,7 @@
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="8">
@@ -5158,7 +5158,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="10">
@@ -5169,7 +5169,7 @@
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="11">
@@ -5180,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="12">
@@ -5191,7 +5191,7 @@
         <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>5.57</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="13">
@@ -5213,7 +5213,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="15">
@@ -5224,7 +5224,7 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -5235,7 +5235,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.56</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="17">
@@ -5268,7 +5268,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="20">
@@ -5276,10 +5276,10 @@
         <v>340</v>
       </c>
       <c r="B20" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C20" t="n">
-        <v>14.47</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="21">
@@ -5312,7 +5312,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="24">
@@ -5323,7 +5323,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="25">
@@ -5331,10 +5331,10 @@
         <v>345</v>
       </c>
       <c r="B25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="n">
-        <v>11.13</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="26">
@@ -5356,7 +5356,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="28">
@@ -5367,7 +5367,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="29">
@@ -5378,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="30">
@@ -5386,10 +5386,10 @@
         <v>350</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>0.74</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="31">
@@ -5400,7 +5400,7 @@
         <v>139</v>
       </c>
       <c r="C31" t="n">
-        <v>25.79</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="32">
@@ -5422,7 +5422,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="34">
@@ -5433,7 +5433,7 @@
         <v>11</v>
       </c>
       <c r="C34" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
     </row>
   </sheetData>
@@ -5521,7 +5521,7 @@
         <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="8">
@@ -5554,7 +5554,7 @@
         <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>3.47</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="11">
@@ -5573,10 +5573,10 @@
         <v>366</v>
       </c>
       <c r="B12" t="n">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C12" t="n">
-        <v>92.08</v>
+        <v>91.94</v>
       </c>
     </row>
     <row r="13">
@@ -5584,10 +5584,10 @@
         <v>367</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>0.97</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="14">
@@ -5598,7 +5598,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
     </row>
   </sheetData>
